--- a/jogos_2025-06-26.xlsx
+++ b/jogos_2025-06-26.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
         <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.13</v>
+        <v>1.76</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="P4" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S4" t="n">
         <v>3.4</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.55</v>
-      </c>
       <c r="T4" t="n">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="U4" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="X4" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.09</v>
+        <v>1.51</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.66</v>
+        <v>2.37</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AD4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['12', '52', '75']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['4', '33']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.93</v>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['26', '53']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['10', '80', '87']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45834.5</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
         <v>3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.76</v>
+        <v>2.13</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.97</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="T5" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="X5" t="n">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.51</v>
+        <v>2.09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.37</v>
+        <v>1.66</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['12', '52', '75']</t>
+          <t>['26', '53']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['4', '33']</t>
+          <t>['10', '80', '87']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.93</v>
+        <v>1.45</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45834.5</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Naftan</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Torpedo BelAZ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Minsk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dinamo Brest</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Naftan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Torpedo BelAZ</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Vitebsk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Dinamo Brest</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vitebsk</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="G14" t="n">
